--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/89.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/89.xlsx
@@ -426,13 +426,13 @@
         <v>-6.800480308870577</v>
       </c>
       <c r="E2">
-        <v>-5.007458971293472</v>
+        <v>-7.180564498840134</v>
       </c>
       <c r="F2">
-        <v>-1.458527342541667</v>
+        <v>-2.24258620133283</v>
       </c>
       <c r="G2">
-        <v>-8.701203901855285</v>
+        <v>-8.915444213746632</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.409020248030183</v>
       </c>
       <c r="E3">
-        <v>-5.692971419724372</v>
+        <v>-7.235150155282356</v>
       </c>
       <c r="F3">
-        <v>-1.595275890130615</v>
+        <v>-2.086306407120675</v>
       </c>
       <c r="G3">
-        <v>-8.693325980051601</v>
+        <v>-8.56895141310326</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.856571310064637</v>
       </c>
       <c r="E4">
-        <v>-6.167816376914669</v>
+        <v>-8.965955289580076</v>
       </c>
       <c r="F4">
-        <v>-1.74143883325238</v>
+        <v>-2.210663406731145</v>
       </c>
       <c r="G4">
-        <v>-7.485418001570399</v>
+        <v>-8.07802047332884</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.188987114986476</v>
       </c>
       <c r="E5">
-        <v>-6.576413460262626</v>
+        <v>-8.805504276467977</v>
       </c>
       <c r="F5">
-        <v>-1.273855255598559</v>
+        <v>-2.062521493884093</v>
       </c>
       <c r="G5">
-        <v>-7.678952498109627</v>
+        <v>-7.431996945747039</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.403192365183057</v>
       </c>
       <c r="E6">
-        <v>-8.452547765238748</v>
+        <v>-9.866691302074917</v>
       </c>
       <c r="F6">
-        <v>-1.177902145862681</v>
+        <v>-2.040170484621757</v>
       </c>
       <c r="G6">
-        <v>-7.71551858685276</v>
+        <v>-6.900854012407997</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.525092912377233</v>
       </c>
       <c r="E7">
-        <v>-9.088612079636238</v>
+        <v>-10.77579603538929</v>
       </c>
       <c r="F7">
-        <v>-1.515928233351256</v>
+        <v>-2.022435966895222</v>
       </c>
       <c r="G7">
-        <v>-6.868431175330961</v>
+        <v>-6.89795347516727</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.570831933006074</v>
       </c>
       <c r="E8">
-        <v>-9.795854129718641</v>
+        <v>-11.77056490548957</v>
       </c>
       <c r="F8">
-        <v>-1.666532054119429</v>
+        <v>-1.996653031483088</v>
       </c>
       <c r="G8">
-        <v>-6.821448215669286</v>
+        <v>-6.683486028496495</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.560914727818537</v>
       </c>
       <c r="E9">
-        <v>-10.88085566906215</v>
+        <v>-12.6927107223639</v>
       </c>
       <c r="F9">
-        <v>-1.502878961654956</v>
+        <v>-2.153550787777731</v>
       </c>
       <c r="G9">
-        <v>-6.414506234763276</v>
+        <v>-5.275020650525971</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5083253363921238</v>
       </c>
       <c r="E10">
-        <v>-10.535673969433</v>
+        <v>-13.37020747293788</v>
       </c>
       <c r="F10">
-        <v>-1.258243015157997</v>
+        <v>-1.904007592786588</v>
       </c>
       <c r="G10">
-        <v>-5.687578343047466</v>
+        <v>-5.044799970992419</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.570430700217647</v>
       </c>
       <c r="E11">
-        <v>-12.03167314827021</v>
+        <v>-14.07950536262607</v>
       </c>
       <c r="F11">
-        <v>-1.470477370694453</v>
+        <v>-1.918832055827088</v>
       </c>
       <c r="G11">
-        <v>-4.369938158657182</v>
+        <v>-4.59245714164695</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.655140459388054</v>
       </c>
       <c r="E12">
-        <v>-14.03877481916348</v>
+        <v>-15.00248182176537</v>
       </c>
       <c r="F12">
-        <v>-1.400123298807288</v>
+        <v>-2.033184033946546</v>
       </c>
       <c r="G12">
-        <v>-3.651208004957468</v>
+        <v>-3.644819512943013</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.71908706186314</v>
       </c>
       <c r="E13">
-        <v>-13.33051523230649</v>
+        <v>-15.51017868053506</v>
       </c>
       <c r="F13">
-        <v>-1.12024611789303</v>
+        <v>-2.051454505382692</v>
       </c>
       <c r="G13">
-        <v>-3.415337674128747</v>
+        <v>-2.771428849665748</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.730753868656085</v>
       </c>
       <c r="E14">
-        <v>-14.41342770635361</v>
+        <v>-16.82458284740547</v>
       </c>
       <c r="F14">
-        <v>-1.353533430971636</v>
+        <v>-2.009019728439482</v>
       </c>
       <c r="G14">
-        <v>-2.616940649231211</v>
+        <v>-2.1588515710407</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.656576033443831</v>
       </c>
       <c r="E15">
-        <v>-16.28151308778222</v>
+        <v>-17.39481876230443</v>
       </c>
       <c r="F15">
-        <v>-1.210625971742873</v>
+        <v>-1.915101917412282</v>
       </c>
       <c r="G15">
-        <v>-1.403837289013693</v>
+        <v>-1.477204433513159</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.465397646070947</v>
       </c>
       <c r="E16">
-        <v>-17.34787916791122</v>
+        <v>-19.01586282770958</v>
       </c>
       <c r="F16">
-        <v>-0.7934410952427778</v>
+        <v>-1.78711087000573</v>
       </c>
       <c r="G16">
-        <v>-1.179576939381653</v>
+        <v>-1.029921227185266</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.135508621395714</v>
       </c>
       <c r="E17">
-        <v>-16.9921815372076</v>
+        <v>-19.29561483612738</v>
       </c>
       <c r="F17">
-        <v>-0.8989833860334628</v>
+        <v>-1.457416501854513</v>
       </c>
       <c r="G17">
-        <v>-0.4284787742413166</v>
+        <v>0.004502773216457341</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.658983115279709</v>
       </c>
       <c r="E18">
-        <v>-17.84258893486817</v>
+        <v>-20.31411100252641</v>
       </c>
       <c r="F18">
-        <v>-0.7616632649365832</v>
+        <v>-1.300934585996075</v>
       </c>
       <c r="G18">
-        <v>-0.3981915262398114</v>
+        <v>0.1074757613791475</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.039770382782526</v>
       </c>
       <c r="E19">
-        <v>-19.88930808858898</v>
+        <v>-20.7376347273758</v>
       </c>
       <c r="F19">
-        <v>-0.2696138560410796</v>
+        <v>-1.390862979611392</v>
       </c>
       <c r="G19">
-        <v>0.303004866785986</v>
+        <v>0.4045811065924306</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.289800103727904</v>
       </c>
       <c r="E20">
-        <v>-19.10341252243697</v>
+        <v>-21.70765461119143</v>
       </c>
       <c r="F20">
-        <v>-0.5663673660525718</v>
+        <v>-1.340592675405102</v>
       </c>
       <c r="G20">
-        <v>-0.08560707634581771</v>
+        <v>0.6316950000625575</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.427870577839147</v>
       </c>
       <c r="E21">
-        <v>-20.75592547005035</v>
+        <v>-22.92128941168753</v>
       </c>
       <c r="F21">
-        <v>-0.02595538307942466</v>
+        <v>-0.9121279199810853</v>
       </c>
       <c r="G21">
-        <v>-0.2108523266152954</v>
+        <v>1.034107339102986</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.470247008646644</v>
       </c>
       <c r="E22">
-        <v>-21.27141375326542</v>
+        <v>-23.35398758035347</v>
       </c>
       <c r="F22">
-        <v>0.264867016328023</v>
+        <v>-0.8664616817995542</v>
       </c>
       <c r="G22">
-        <v>0.3073073738721407</v>
+        <v>1.322312656005164</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.428718143380512</v>
       </c>
       <c r="E23">
-        <v>-22.41850580191511</v>
+        <v>-23.7293423602575</v>
       </c>
       <c r="F23">
-        <v>0.1417972996615032</v>
+        <v>-0.8381687931569372</v>
       </c>
       <c r="G23">
-        <v>-0.3962674074761609</v>
+        <v>1.347407133014945</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.314843074572274</v>
       </c>
       <c r="E24">
-        <v>-23.05398866672713</v>
+        <v>-24.13168055413893</v>
       </c>
       <c r="F24">
-        <v>0.5603108774756891</v>
+        <v>-0.5538333388808124</v>
       </c>
       <c r="G24">
-        <v>0.4982781192228953</v>
+        <v>1.32854189259956</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.136097983666764</v>
       </c>
       <c r="E25">
-        <v>-22.18019453609645</v>
+        <v>-24.64086841577424</v>
       </c>
       <c r="F25">
-        <v>0.3162846093871911</v>
+        <v>-0.5739651518710488</v>
       </c>
       <c r="G25">
-        <v>0.8374712779895156</v>
+        <v>1.359523598662302</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.896324422965098</v>
       </c>
       <c r="E26">
-        <v>-22.68265004217421</v>
+        <v>-24.25648455445003</v>
       </c>
       <c r="F26">
-        <v>0.4496385073594667</v>
+        <v>-0.6314414241142925</v>
       </c>
       <c r="G26">
-        <v>0.8978369144252369</v>
+        <v>0.7725759996882127</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.602987670789832</v>
       </c>
       <c r="E27">
-        <v>-23.6947004245971</v>
+        <v>-25.31564065971913</v>
       </c>
       <c r="F27">
-        <v>0.5032868938343739</v>
+        <v>-0.3041493214311938</v>
       </c>
       <c r="G27">
-        <v>0.245714687478596</v>
+        <v>0.9903851994356119</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.273031444415266</v>
       </c>
       <c r="E28">
-        <v>-22.81777477262751</v>
+        <v>-24.53320471860071</v>
       </c>
       <c r="F28">
-        <v>0.2877183595016501</v>
+        <v>-0.5846047027926057</v>
       </c>
       <c r="G28">
-        <v>0.1054106624075769</v>
+        <v>0.7149385913502047</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.926671088850695</v>
       </c>
       <c r="E29">
-        <v>-22.74604050662506</v>
+        <v>-24.57861177801506</v>
       </c>
       <c r="F29">
-        <v>0.4282003589750155</v>
+        <v>-0.5427489546639522</v>
       </c>
       <c r="G29">
-        <v>0.1785506721276156</v>
+        <v>0.771476876215354</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.583878624129927</v>
       </c>
       <c r="E30">
-        <v>-22.5428571021918</v>
+        <v>-24.66445034967662</v>
       </c>
       <c r="F30">
-        <v>0.7734920569535446</v>
+        <v>-0.3424149252361142</v>
       </c>
       <c r="G30">
-        <v>-0.1881388486726098</v>
+        <v>0.3750118133534815</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.274636795636365</v>
       </c>
       <c r="E31">
-        <v>-22.63376259166965</v>
+        <v>-24.29823678789854</v>
       </c>
       <c r="F31">
-        <v>0.819731525377813</v>
+        <v>-0.3450416782703914</v>
       </c>
       <c r="G31">
-        <v>-0.6662993312795992</v>
+        <v>0.3308484578502092</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.023813006123163</v>
       </c>
       <c r="E32">
-        <v>-22.6174944629103</v>
+        <v>-24.19136635408805</v>
       </c>
       <c r="F32">
-        <v>0.5427461750667283</v>
+        <v>-0.3209171343986614</v>
       </c>
       <c r="G32">
-        <v>-0.3388884628526732</v>
+        <v>0.2571158091079878</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.848621128867912</v>
       </c>
       <c r="E33">
-        <v>-21.25409486204088</v>
+        <v>-23.8072109193867</v>
       </c>
       <c r="F33">
-        <v>0.1533381143173059</v>
+        <v>-0.4000361617748478</v>
       </c>
       <c r="G33">
-        <v>-0.2718549847312484</v>
+        <v>-0.06124621856613965</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.76678440192849</v>
       </c>
       <c r="E34">
-        <v>-21.59433008698216</v>
+        <v>-23.78918182902563</v>
       </c>
       <c r="F34">
-        <v>0.683656440487341</v>
+        <v>-0.4044223671726712</v>
       </c>
       <c r="G34">
-        <v>-1.245169286488784</v>
+        <v>0.1392067511395384</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.787042073113073</v>
       </c>
       <c r="E35">
-        <v>-21.43164049296598</v>
+        <v>-22.98450544126274</v>
       </c>
       <c r="F35">
-        <v>0.3894054283997063</v>
+        <v>-0.35483546607369</v>
       </c>
       <c r="G35">
-        <v>-0.6804417347296599</v>
+        <v>-0.2335370863674787</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.905484001532467</v>
       </c>
       <c r="E36">
-        <v>-20.85348025085925</v>
+        <v>-21.89823301925384</v>
       </c>
       <c r="F36">
-        <v>0.4598481355989706</v>
+        <v>-0.173936592650334</v>
       </c>
       <c r="G36">
-        <v>-0.7546834786671484</v>
+        <v>-0.169615615798661</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.110413258492533</v>
       </c>
       <c r="E37">
-        <v>-19.46240364972117</v>
+        <v>-22.37437377837748</v>
       </c>
       <c r="F37">
-        <v>0.5502942588410374</v>
+        <v>-0.2119280068449277</v>
       </c>
       <c r="G37">
-        <v>-0.6963672767354508</v>
+        <v>0.03893327288405935</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.387222572537246</v>
       </c>
       <c r="E38">
-        <v>-19.14108630236449</v>
+        <v>-21.14015566255554</v>
       </c>
       <c r="F38">
-        <v>0.1665886792924868</v>
+        <v>-0.2472669886157574</v>
       </c>
       <c r="G38">
-        <v>-0.9508574379879917</v>
+        <v>-0.2823397350091594</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.709011867169325</v>
       </c>
       <c r="E39">
-        <v>-19.2099216268622</v>
+        <v>-20.87940874916015</v>
       </c>
       <c r="F39">
-        <v>0.7467490437215654</v>
+        <v>-0.1030780450148642</v>
       </c>
       <c r="G39">
-        <v>-0.651546013595218</v>
+        <v>-0.2068683303692565</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.039080905825476</v>
       </c>
       <c r="E40">
-        <v>-17.29159900124847</v>
+        <v>-19.40623561976419</v>
       </c>
       <c r="F40">
-        <v>0.6439304249512852</v>
+        <v>-0.08279546915731834</v>
       </c>
       <c r="G40">
-        <v>-0.2077350975735061</v>
+        <v>-0.4770882277832549</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.345635924723989</v>
       </c>
       <c r="E41">
-        <v>-17.59033533863206</v>
+        <v>-20.11242275417009</v>
       </c>
       <c r="F41">
-        <v>0.893799168331728</v>
+        <v>0.05848673322715134</v>
       </c>
       <c r="G41">
-        <v>-0.6277177477121271</v>
+        <v>-0.86863464783547</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.593468778590466</v>
       </c>
       <c r="E42">
-        <v>-17.75848225232907</v>
+        <v>-19.06430173139106</v>
       </c>
       <c r="F42">
-        <v>1.070291127172191</v>
+        <v>-0.2363930097192083</v>
       </c>
       <c r="G42">
-        <v>-0.7522607076865953</v>
+        <v>-0.530877398593962</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.749532292683114</v>
       </c>
       <c r="E43">
-        <v>-17.04787610107356</v>
+        <v>-18.02057895940502</v>
       </c>
       <c r="F43">
-        <v>0.5445238515131361</v>
+        <v>-0.2064334458621586</v>
       </c>
       <c r="G43">
-        <v>-1.791590297175021</v>
+        <v>-0.6487890673070024</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.792108214272246</v>
       </c>
       <c r="E44">
-        <v>-15.21239758175618</v>
+        <v>-18.00362139756575</v>
       </c>
       <c r="F44">
-        <v>0.8095260389753232</v>
+        <v>0.1798591250853349</v>
       </c>
       <c r="G44">
-        <v>-0.7339202269340244</v>
+        <v>-1.029451293158866</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.711589192640952</v>
       </c>
       <c r="E45">
-        <v>-14.44599303635159</v>
+        <v>-16.93125808028369</v>
       </c>
       <c r="F45">
-        <v>0.6143717909171904</v>
+        <v>0.08624698162976838</v>
       </c>
       <c r="G45">
-        <v>-1.279542349775381</v>
+        <v>-0.8182472772269835</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.509316403623805</v>
       </c>
       <c r="E46">
-        <v>-13.45434322795626</v>
+        <v>-15.68887059778581</v>
       </c>
       <c r="F46">
-        <v>0.9176230148362418</v>
+        <v>0.2679187218399364</v>
       </c>
       <c r="G46">
-        <v>-1.36023263285292</v>
+        <v>-0.961809511547712</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.197152635958434</v>
       </c>
       <c r="E47">
-        <v>-13.11880943823468</v>
+        <v>-15.50237064324438</v>
       </c>
       <c r="F47">
-        <v>0.3578578842314899</v>
+        <v>0.2989667604642646</v>
       </c>
       <c r="G47">
-        <v>-1.391002868603781</v>
+        <v>-1.449507044146038</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.800096538574643</v>
       </c>
       <c r="E48">
-        <v>-12.74255756468449</v>
+        <v>-14.53969363705105</v>
       </c>
       <c r="F48">
-        <v>0.8921490604653514</v>
+        <v>0.1477880527185493</v>
       </c>
       <c r="G48">
-        <v>-2.324819215442363</v>
+        <v>-1.860453907254816</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.346225709881558</v>
       </c>
       <c r="E49">
-        <v>-13.12032536036825</v>
+        <v>-13.73977682946642</v>
       </c>
       <c r="F49">
-        <v>0.2697510705349289</v>
+        <v>0.3060360478797556</v>
       </c>
       <c r="G49">
-        <v>-1.139551614055296</v>
+        <v>-2.035433841985002</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.861239424833616</v>
       </c>
       <c r="E50">
-        <v>-12.06416372046435</v>
+        <v>-13.41511199378193</v>
       </c>
       <c r="F50">
-        <v>0.8260271176390892</v>
+        <v>0.3202392353681559</v>
       </c>
       <c r="G50">
-        <v>-2.145043342898302</v>
+        <v>-2.067689591408207</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.374894170935836</v>
       </c>
       <c r="E51">
-        <v>-10.7469104506251</v>
+        <v>-12.43325130447921</v>
       </c>
       <c r="F51">
-        <v>0.7557070088154392</v>
+        <v>0.2797900550894561</v>
       </c>
       <c r="G51">
-        <v>-2.137887291974061</v>
+        <v>-2.168493050815682</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.913009979608392</v>
       </c>
       <c r="E52">
-        <v>-11.0139494791776</v>
+        <v>-11.91135876940126</v>
       </c>
       <c r="F52">
-        <v>0.422690887378996</v>
+        <v>0.2233467569975033</v>
       </c>
       <c r="G52">
-        <v>-2.319524625411585</v>
+        <v>-2.867901083796566</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.494243496227817</v>
       </c>
       <c r="E53">
-        <v>-10.88086812869612</v>
+        <v>-10.63658869820368</v>
       </c>
       <c r="F53">
-        <v>0.1742519061357851</v>
+        <v>-0.06367177929628895</v>
       </c>
       <c r="G53">
-        <v>-2.849842563459836</v>
+        <v>-2.846182299543095</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.132367792396537</v>
       </c>
       <c r="E54">
-        <v>-8.55652341075583</v>
+        <v>-10.47494156023003</v>
       </c>
       <c r="F54">
-        <v>0.2840718861945267</v>
+        <v>0.3362002184852968</v>
       </c>
       <c r="G54">
-        <v>-2.937673232994069</v>
+        <v>-3.493145695177696</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.835727681948264</v>
       </c>
       <c r="E55">
-        <v>-9.844662669208027</v>
+        <v>-10.06020603054398</v>
       </c>
       <c r="F55">
-        <v>0.3225843434854813</v>
+        <v>0.3493199014108354</v>
       </c>
       <c r="G55">
-        <v>-3.376672546734359</v>
+        <v>-3.510778664146075</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.60265949500215</v>
       </c>
       <c r="E56">
-        <v>-8.347388454494089</v>
+        <v>-9.610147438540258</v>
       </c>
       <c r="F56">
-        <v>0.2557748557148956</v>
+        <v>0.1847108729635316</v>
       </c>
       <c r="G56">
-        <v>-2.584335060032797</v>
+        <v>-3.858226997309796</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.421716231499561</v>
       </c>
       <c r="E57">
-        <v>-7.635536339841126</v>
+        <v>-8.735921373931799</v>
       </c>
       <c r="F57">
-        <v>0.9357990523884685</v>
+        <v>0.2872064284467201</v>
       </c>
       <c r="G57">
-        <v>-3.467513404782146</v>
+        <v>-3.967392671642607</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.281046951472514</v>
       </c>
       <c r="E58">
-        <v>-7.381297508591747</v>
+        <v>-8.350553201523608</v>
       </c>
       <c r="F58">
-        <v>0.4622752520891731</v>
+        <v>0.3486862003476938</v>
       </c>
       <c r="G58">
-        <v>-4.455497480397146</v>
+        <v>-4.531616349695645</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.165156439699065</v>
       </c>
       <c r="E59">
-        <v>-7.285424778369405</v>
+        <v>-7.535215520289893</v>
       </c>
       <c r="F59">
-        <v>0.5619237088089397</v>
+        <v>0.1744142661467337</v>
       </c>
       <c r="G59">
-        <v>-3.887945102990438</v>
+        <v>-4.284047272354146</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.056234339634767</v>
       </c>
       <c r="E60">
-        <v>-5.711843611984393</v>
+        <v>-7.153647536243921</v>
       </c>
       <c r="F60">
-        <v>0.287487244996269</v>
+        <v>-0.01306515792446156</v>
       </c>
       <c r="G60">
-        <v>-4.432940647129928</v>
+        <v>-4.65279667063676</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.940101449271078</v>
       </c>
       <c r="E61">
-        <v>-6.155880047567112</v>
+        <v>-6.56744667701232</v>
       </c>
       <c r="F61">
-        <v>0.05598754877290523</v>
+        <v>0.03185637796195284</v>
       </c>
       <c r="G61">
-        <v>-4.805287651459095</v>
+        <v>-5.091412204922157</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.804778226967955</v>
       </c>
       <c r="E62">
-        <v>-5.946138722451946</v>
+        <v>-6.592000462364707</v>
       </c>
       <c r="F62">
-        <v>0.3490407415960919</v>
+        <v>0.05747115479131915</v>
       </c>
       <c r="G62">
-        <v>-3.885316083187187</v>
+        <v>-4.97153986702119</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.642420298605376</v>
       </c>
       <c r="E63">
-        <v>-4.514800890730986</v>
+        <v>-5.687705147764489</v>
       </c>
       <c r="F63">
-        <v>0.2828450740709806</v>
+        <v>0.1530481857263261</v>
       </c>
       <c r="G63">
-        <v>-4.746668603154829</v>
+        <v>-5.403432733984469</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.450951845602306</v>
       </c>
       <c r="E64">
-        <v>-4.067628780598022</v>
+        <v>-5.673933099011358</v>
       </c>
       <c r="F64">
-        <v>0.4352679896557008</v>
+        <v>-0.2078267598336673</v>
       </c>
       <c r="G64">
-        <v>-4.831611789171291</v>
+        <v>-5.133092742319279</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.231814711532023</v>
       </c>
       <c r="E65">
-        <v>-4.810683971934421</v>
+        <v>-4.94318802604175</v>
       </c>
       <c r="F65">
-        <v>-0.08100288209766021</v>
+        <v>-0.06826093470779822</v>
       </c>
       <c r="G65">
-        <v>-4.624190742151931</v>
+        <v>-5.633932763189271</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.9854663318709782</v>
       </c>
       <c r="E66">
-        <v>-4.662655213894881</v>
+        <v>-5.01985215388676</v>
       </c>
       <c r="F66">
-        <v>-0.12892642145182</v>
+        <v>0.07159067717203672</v>
       </c>
       <c r="G66">
-        <v>-4.953674541784202</v>
+        <v>-5.382442347471919</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.7117042909126124</v>
       </c>
       <c r="E67">
-        <v>-5.552015580571016</v>
+        <v>-4.319928062158706</v>
       </c>
       <c r="F67">
-        <v>0.5844097419579323</v>
+        <v>-0.496603920123603</v>
       </c>
       <c r="G67">
-        <v>-5.135061243740979</v>
+        <v>-5.847212321071088</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.4102893731248315</v>
       </c>
       <c r="E68">
-        <v>-4.208904417023389</v>
+        <v>-4.800134815169356</v>
       </c>
       <c r="F68">
-        <v>0.134055377914939</v>
+        <v>-0.1007138844472744</v>
       </c>
       <c r="G68">
-        <v>-5.036093137781057</v>
+        <v>-5.823846156980624</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.08256166154845043</v>
       </c>
       <c r="E69">
-        <v>-3.713700417918783</v>
+        <v>-4.540779227567788</v>
       </c>
       <c r="F69">
-        <v>0.0133150303850915</v>
+        <v>-0.2454503789014181</v>
       </c>
       <c r="G69">
-        <v>-4.792672533594836</v>
+        <v>-5.78767429067075</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.2667959709541691</v>
       </c>
       <c r="E70">
-        <v>-3.577965165400737</v>
+        <v>-4.498096674782525</v>
       </c>
       <c r="F70">
-        <v>-0.09859906246792731</v>
+        <v>-0.3490725140524138</v>
       </c>
       <c r="G70">
-        <v>-4.841960780730464</v>
+        <v>-5.037228811678191</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.6310568586223881</v>
       </c>
       <c r="E71">
-        <v>-2.792783951596601</v>
+        <v>-4.134769594875199</v>
       </c>
       <c r="F71">
-        <v>0.1077886759395695</v>
+        <v>-0.2715265563741437</v>
       </c>
       <c r="G71">
-        <v>-4.979197180906925</v>
+        <v>-5.767910954116022</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.002963875974</v>
       </c>
       <c r="E72">
-        <v>-3.058194921309769</v>
+        <v>-4.590941713949067</v>
       </c>
       <c r="F72">
-        <v>0.009109409081078412</v>
+        <v>-0.256250633099118</v>
       </c>
       <c r="G72">
-        <v>-5.209551008414623</v>
+        <v>-5.287142337662511</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.3732788811136</v>
       </c>
       <c r="E73">
-        <v>-4.275443015658468</v>
+        <v>-4.339975613223653</v>
       </c>
       <c r="F73">
-        <v>-0.2605407478782167</v>
+        <v>-0.4170483431261413</v>
       </c>
       <c r="G73">
-        <v>-5.266700207514093</v>
+        <v>-4.9165706396553</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.730328337810605</v>
       </c>
       <c r="E74">
-        <v>-5.247788697816</v>
+        <v>-4.907113232474289</v>
       </c>
       <c r="F74">
-        <v>-0.3111945861920036</v>
+        <v>-0.1400132907708886</v>
       </c>
       <c r="G74">
-        <v>-4.307434322401339</v>
+        <v>-5.207256163919035</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.062300547224242</v>
       </c>
       <c r="E75">
-        <v>-4.246956139181468</v>
+        <v>-4.992316362803147</v>
       </c>
       <c r="F75">
-        <v>-0.7282113041093308</v>
+        <v>-0.5461767389767366</v>
       </c>
       <c r="G75">
-        <v>-4.945693495569168</v>
+        <v>-4.956214796271355</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.358021541032394</v>
       </c>
       <c r="E76">
-        <v>-5.126290653719466</v>
+        <v>-5.421176964204943</v>
       </c>
       <c r="F76">
-        <v>-0.305813511543418</v>
+        <v>-0.2135474651174007</v>
       </c>
       <c r="G76">
-        <v>-3.966886187191931</v>
+        <v>-5.153453939385372</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.609230004010902</v>
       </c>
       <c r="E77">
-        <v>-5.77730652888634</v>
+        <v>-6.343954069200647</v>
       </c>
       <c r="F77">
-        <v>-0.2742336610464925</v>
+        <v>-0.6004588265147854</v>
       </c>
       <c r="G77">
-        <v>-3.471429521668816</v>
+        <v>-4.459559798980918</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.811288465564566</v>
       </c>
       <c r="E78">
-        <v>-5.530796823912467</v>
+        <v>-6.263547897951967</v>
       </c>
       <c r="F78">
-        <v>-0.6518159487535491</v>
+        <v>-0.3097441148697017</v>
       </c>
       <c r="G78">
-        <v>-3.932460909013511</v>
+        <v>-4.289078177181222</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.9612976357934</v>
       </c>
       <c r="E79">
-        <v>-7.21201676820306</v>
+        <v>-7.243199078829873</v>
       </c>
       <c r="F79">
-        <v>-0.7417965295152427</v>
+        <v>-0.4306269415928308</v>
       </c>
       <c r="G79">
-        <v>-3.538165374906853</v>
+        <v>-4.026322398553216</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.057874665167874</v>
       </c>
       <c r="E80">
-        <v>-6.70589397652548</v>
+        <v>-7.310065781159613</v>
       </c>
       <c r="F80">
-        <v>-0.3475955349732223</v>
+        <v>-0.4169887006731397</v>
       </c>
       <c r="G80">
-        <v>-3.434678070059714</v>
+        <v>-3.534408513440241</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.102170141036143</v>
       </c>
       <c r="E81">
-        <v>-8.043036975399328</v>
+        <v>-8.04431201127605</v>
       </c>
       <c r="F81">
-        <v>-0.0302537815325513</v>
+        <v>-0.2570988813195847</v>
       </c>
       <c r="G81">
-        <v>-3.233018936352941</v>
+        <v>-3.802464103588207</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.099397307108766</v>
       </c>
       <c r="E82">
-        <v>-8.999392793956272</v>
+        <v>-9.203435913133774</v>
       </c>
       <c r="F82">
-        <v>-0.3931938470277239</v>
+        <v>-0.6114843966460468</v>
       </c>
       <c r="G82">
-        <v>-3.020324185259534</v>
+        <v>-3.589312472191354</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.057837329524114</v>
       </c>
       <c r="E83">
-        <v>-10.15061728787417</v>
+        <v>-10.06652306496904</v>
       </c>
       <c r="F83">
-        <v>-0.7003955550907262</v>
+        <v>-0.2665306725678599</v>
       </c>
       <c r="G83">
-        <v>-2.868887945252007</v>
+        <v>-2.917191941676785</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.98762615987509</v>
       </c>
       <c r="E84">
-        <v>-11.10775391016018</v>
+        <v>-11.19891274552884</v>
       </c>
       <c r="F84">
-        <v>-0.4924049257588123</v>
+        <v>-0.3340252201805608</v>
       </c>
       <c r="G84">
-        <v>-2.451113985037468</v>
+        <v>-3.106478756766272</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.903480946583442</v>
       </c>
       <c r="E85">
-        <v>-11.67168525026805</v>
+        <v>-12.68945045147391</v>
       </c>
       <c r="F85">
-        <v>-0.274619680256197</v>
+        <v>-0.1241492266398753</v>
       </c>
       <c r="G85">
-        <v>-2.609163241094284</v>
+        <v>-2.687715324351701</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.819986956803866</v>
       </c>
       <c r="E86">
-        <v>-13.01170227137868</v>
+        <v>-13.43258040061415</v>
       </c>
       <c r="F86">
-        <v>-0.7241953789405587</v>
+        <v>-0.4688039100856516</v>
       </c>
       <c r="G86">
-        <v>-2.377752062027185</v>
+        <v>-2.686323797484637</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.749827205625468</v>
       </c>
       <c r="E87">
-        <v>-14.18496785779744</v>
+        <v>-15.19841371922548</v>
       </c>
       <c r="F87">
-        <v>-0.1460802536289922</v>
+        <v>-0.3101715524495463</v>
       </c>
       <c r="G87">
-        <v>-1.916556197773249</v>
+        <v>-2.344778357841424</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.708961173774322</v>
       </c>
       <c r="E88">
-        <v>-17.47513771611529</v>
+        <v>-16.87666411741882</v>
       </c>
       <c r="F88">
-        <v>-0.215000421541911</v>
+        <v>-0.5012908228886426</v>
       </c>
       <c r="G88">
-        <v>-1.75406606516695</v>
+        <v>-2.340110346512513</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.711353658251378</v>
       </c>
       <c r="E89">
-        <v>-16.85184037333032</v>
+        <v>-17.48442429663761</v>
       </c>
       <c r="F89">
-        <v>-0.4136959402470117</v>
+        <v>-0.1511929372390707</v>
       </c>
       <c r="G89">
-        <v>-2.231205746638814</v>
+        <v>-2.0517979890821</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.767006817921475</v>
       </c>
       <c r="E90">
-        <v>-18.96012673173038</v>
+        <v>-19.79616401820704</v>
       </c>
       <c r="F90">
-        <v>-0.4374800251161911</v>
+        <v>-0.4282081087766562</v>
       </c>
       <c r="G90">
-        <v>-1.440828929125178</v>
+        <v>-1.720126385482477</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.883322043421125</v>
       </c>
       <c r="E91">
-        <v>-21.4812921343543</v>
+        <v>-20.73057426812359</v>
       </c>
       <c r="F91">
-        <v>-0.3052328259940556</v>
+        <v>-0.3450541037814334</v>
       </c>
       <c r="G91">
-        <v>-1.022036778520104</v>
+        <v>-2.046988997545269</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.063666045237142</v>
       </c>
       <c r="E92">
-        <v>-22.76908667626654</v>
+        <v>-23.3798537804845</v>
       </c>
       <c r="F92">
-        <v>-0.3826387895812526</v>
+        <v>-0.3336010960703275</v>
       </c>
       <c r="G92">
-        <v>-1.526941728718458</v>
+        <v>-1.970019025510067</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.30152843533669</v>
       </c>
       <c r="E93">
-        <v>-24.34671722369326</v>
+        <v>-25.89996011422059</v>
       </c>
       <c r="F93">
-        <v>-0.5723796566620906</v>
+        <v>-0.5349391067903585</v>
       </c>
       <c r="G93">
-        <v>-1.354603867514479</v>
+        <v>-1.920762107309533</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.580360739634354</v>
       </c>
       <c r="E94">
-        <v>-27.92389890382471</v>
+        <v>-27.44652464093759</v>
       </c>
       <c r="F94">
-        <v>-0.4415713317186178</v>
+        <v>-0.4664662572749513</v>
       </c>
       <c r="G94">
-        <v>-2.345746944084727</v>
+        <v>-1.988187197119625</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.884877258968722</v>
       </c>
       <c r="E95">
-        <v>-29.86066178772067</v>
+        <v>-30.31847027205653</v>
       </c>
       <c r="F95">
-        <v>-0.3754030003177989</v>
+        <v>-0.4744931374080786</v>
       </c>
       <c r="G95">
-        <v>-2.016602541249302</v>
+        <v>-2.145951882016009</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.193614197765166</v>
       </c>
       <c r="E96">
-        <v>-32.48846504432089</v>
+        <v>-32.11965572546479</v>
       </c>
       <c r="F96">
-        <v>-0.8939659646747062</v>
+        <v>-0.558181439378107</v>
       </c>
       <c r="G96">
-        <v>-2.246891100142222</v>
+        <v>-2.107291976110804</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.483464074235761</v>
       </c>
       <c r="E97">
-        <v>-34.81252942049676</v>
+        <v>-34.97235122209315</v>
       </c>
       <c r="F97">
-        <v>-0.8493939998322733</v>
+        <v>-0.5590619939272828</v>
       </c>
       <c r="G97">
-        <v>-2.740353156797727</v>
+        <v>-2.498859282119748</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.734640831191813</v>
       </c>
       <c r="E98">
-        <v>-37.26223674567134</v>
+        <v>-37.43416931149093</v>
       </c>
       <c r="F98">
-        <v>-0.4854449828404908</v>
+        <v>-0.6979924612552048</v>
       </c>
       <c r="G98">
-        <v>-2.54492064894076</v>
+        <v>-2.426288414720572</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.932869354989867</v>
       </c>
       <c r="E99">
-        <v>-40.01904705244338</v>
+        <v>-39.77761257170845</v>
       </c>
       <c r="F99">
-        <v>-1.218347184304367</v>
+        <v>-0.7419721434046361</v>
       </c>
       <c r="G99">
-        <v>-1.89889973210355</v>
+        <v>-2.607599405084208</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.061153192912694</v>
       </c>
       <c r="E100">
-        <v>-42.48274862317697</v>
+        <v>-41.82197270139675</v>
       </c>
       <c r="F100">
-        <v>-0.7196352163881474</v>
+        <v>-0.8914800340989049</v>
       </c>
       <c r="G100">
-        <v>-2.311509639516867</v>
+        <v>-2.54827545574034</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.118598274810938</v>
       </c>
       <c r="E101">
-        <v>-45.97152712365378</v>
+        <v>-44.24764331602888</v>
       </c>
       <c r="F101">
-        <v>-1.431601260113669</v>
+        <v>-1.077115512331468</v>
       </c>
       <c r="G101">
-        <v>-2.542996530177109</v>
+        <v>-2.808378717863774</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.101626959706659</v>
       </c>
       <c r="E102">
-        <v>-48.36987583758552</v>
+        <v>-47.08904623106503</v>
       </c>
       <c r="F102">
-        <v>-1.493394154892901</v>
+        <v>-1.09700627040749</v>
       </c>
       <c r="G102">
-        <v>-3.131513186650457</v>
+        <v>-3.31042490273486</v>
       </c>
     </row>
   </sheetData>
